--- a/Hardhare/StepMotor_2Routes_TMC5160/BOM/StepMotor_TMC5160.xlsx
+++ b/Hardhare/StepMotor_2Routes_TMC5160/BOM/StepMotor_TMC5160.xlsx
@@ -10,7 +10,7 @@
     <sheet name="StepMotor_TMC5160" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">StepMotor_TMC5160!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">StepMotor_TMC5160!$A$1:$F$45</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -609,7 +609,7 @@
     <t>A00500178</t>
   </si>
   <si>
-    <t>https://item.szlcsc.com/48788257.html?fromZone=s_s__%2522500mr%25203w%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D</t>
+    <t>https://item.szlcsc.com/3159229.html?fromZone=s_s__%252250mr%25203w%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D</t>
   </si>
   <si>
     <t>0R/NC</t>
@@ -1858,13 +1858,6 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -2151,7 +2144,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:I45"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.85"/>
   <cols>
@@ -2188,7 +2181,7 @@
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" hidden="1" spans="1:9">
+    <row r="2" spans="1:9">
       <c r="A2" s="18" t="s">
         <v>8</v>
       </c>
@@ -2214,7 +2207,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:9">
+    <row r="3" spans="1:9">
       <c r="A3" s="18" t="s">
         <v>15</v>
       </c>
@@ -2265,7 +2258,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" hidden="1" spans="1:9">
+    <row r="5" spans="1:9">
       <c r="A5" s="18" t="s">
         <v>23</v>
       </c>
@@ -2316,7 +2309,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" hidden="1" spans="1:9">
+    <row r="7" spans="1:9">
       <c r="A7" s="18" t="s">
         <v>31</v>
       </c>
@@ -2504,7 +2497,7 @@
       </c>
       <c r="I13" s="3"/>
     </row>
-    <row r="14" hidden="1" spans="1:9">
+    <row r="14" spans="1:9">
       <c r="A14" s="18" t="s">
         <v>77</v>
       </c>
@@ -2555,7 +2548,7 @@
       </c>
       <c r="I15" s="3"/>
     </row>
-    <row r="16" hidden="1" spans="1:9">
+    <row r="16" spans="1:9">
       <c r="A16" s="18" t="s">
         <v>83</v>
       </c>
@@ -2579,7 +2572,7 @@
       </c>
       <c r="I16" s="3"/>
     </row>
-    <row r="17" hidden="1" spans="1:9">
+    <row r="17" spans="1:9">
       <c r="A17" s="18" t="s">
         <v>93</v>
       </c>
@@ -2630,7 +2623,7 @@
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" hidden="1" spans="1:9">
+    <row r="19" spans="1:9">
       <c r="A19" s="18" t="s">
         <v>106</v>
       </c>
@@ -2681,7 +2674,7 @@
       </c>
       <c r="I20" s="3"/>
     </row>
-    <row r="21" hidden="1" spans="1:9">
+    <row r="21" spans="1:9">
       <c r="A21" s="18" t="s">
         <v>119</v>
       </c>
@@ -2759,7 +2752,7 @@
       </c>
       <c r="I23" s="3"/>
     </row>
-    <row r="24" hidden="1" spans="1:9">
+    <row r="24" spans="1:9">
       <c r="A24" s="18" t="s">
         <v>133</v>
       </c>
@@ -2804,12 +2797,12 @@
       <c r="G25" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="H25" s="8" t="s">
+      <c r="H25" s="11" t="s">
         <v>139</v>
       </c>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" hidden="1" spans="1:9">
+    <row r="26" spans="1:9">
       <c r="A26" s="18" t="s">
         <v>140</v>
       </c>
@@ -2832,7 +2825,7 @@
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" hidden="1" spans="1:9">
+    <row r="27" spans="1:9">
       <c r="A27" s="18" t="s">
         <v>142</v>
       </c>
@@ -2856,7 +2849,7 @@
       </c>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" hidden="1" spans="1:9">
+    <row r="28" spans="1:9">
       <c r="A28" s="18" t="s">
         <v>145</v>
       </c>
@@ -2880,7 +2873,7 @@
       </c>
       <c r="I28" s="3"/>
     </row>
-    <row r="29" hidden="1" spans="1:9">
+    <row r="29" spans="1:9">
       <c r="A29" s="18" t="s">
         <v>148</v>
       </c>
@@ -2904,7 +2897,7 @@
       </c>
       <c r="I29" s="3"/>
     </row>
-    <row r="30" hidden="1" spans="1:9">
+    <row r="30" spans="1:9">
       <c r="A30" s="18" t="s">
         <v>151</v>
       </c>
@@ -2957,7 +2950,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="32" hidden="1" spans="1:9">
+    <row r="32" spans="1:9">
       <c r="A32" s="18" t="s">
         <v>140</v>
       </c>
@@ -2980,7 +2973,7 @@
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" hidden="1" spans="1:9">
+    <row r="33" spans="1:9">
       <c r="A33" s="18" t="s">
         <v>161</v>
       </c>
@@ -3004,7 +2997,7 @@
       </c>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" hidden="1" spans="1:9">
+    <row r="34" spans="1:9">
       <c r="A34" s="18" t="s">
         <v>164</v>
       </c>
@@ -3054,7 +3047,7 @@
       </c>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" hidden="1" spans="1:9">
+    <row r="36" spans="1:9">
       <c r="A36" s="18" t="s">
         <v>173</v>
       </c>
@@ -3159,7 +3152,7 @@
       </c>
       <c r="I39" s="3"/>
     </row>
-    <row r="40" hidden="1" spans="1:9">
+    <row r="40" spans="1:9">
       <c r="A40" s="18" t="s">
         <v>193</v>
       </c>
@@ -3183,7 +3176,7 @@
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" hidden="1" spans="1:9">
+    <row r="41" spans="1:9">
       <c r="A41" s="18" t="s">
         <v>197</v>
       </c>
@@ -3207,7 +3200,7 @@
       </c>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" hidden="1" spans="1:9">
+    <row r="42" spans="1:9">
       <c r="A42" s="18" t="s">
         <v>201</v>
       </c>
@@ -3231,7 +3224,7 @@
       </c>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" hidden="1" spans="1:9">
+    <row r="43" spans="1:9">
       <c r="A43" s="18" t="s">
         <v>207</v>
       </c>
@@ -3274,10 +3267,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F43" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="5">
-      <colorFilter dxfId="0"/>
-    </filterColumn>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:F45" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <hyperlinks>
@@ -3293,15 +3283,15 @@
     <hyperlink ref="H20" r:id="rId10" display="https://item.szlcsc.com/461587.html?fromZone=s_s__%2522aod4126%2522&amp;spm=sc.gbn.xh1.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
     <hyperlink ref="H22" r:id="rId11" display="https://item.szlcsc.com/2177928.html?fromZone=s_s__%25222.2r%25200603%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
     <hyperlink ref="H23" r:id="rId12" display="https://item.szlcsc.com/3180687.html?fromZone=s_s__%252247r%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
-    <hyperlink ref="H25" r:id="rId13" display="https://item.szlcsc.com/48788257.html?fromZone=s_s__%2522500mr%25203w%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
-    <hyperlink ref="H35" r:id="rId14" display="https://item.szlcsc.com/532372.html?fromZone=s_s__%2522TMC5160%2522&amp;spm=sc.gbn.xh1.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
-    <hyperlink ref="H37" r:id="rId15" display="https://item.szlcsc.com/8568600.html?fromZone=s_s__%2522XDDB-1518%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
-    <hyperlink ref="H38" r:id="rId16" display="https://item.szlcsc.com/44273613.html?fromZone=s_s__%2522XL1509%2522&amp;spm=sc.gbn.xh1.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
-    <hyperlink ref="H39" r:id="rId17" display="https://item.szlcsc.com/545744.html?fromZone=s_s__%2522AM26LV32%2522&amp;spm=sc.gbn.xh1.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
-    <hyperlink ref="I9" r:id="rId18" display="https://item.szlcsc.com/54596843.html?fromZone=s_s__%2522470uF%252F50V%2522&amp;spm=sc.gbn.xh4.zy.n___sc.gbn.hd.ss&amp;lcsc_vid=EwQLVQJfFVFYVFdUEwcMBlJTRwMNA1IFEQMIXgcCQFExVlNeRVZcVldUQ1RZVTsOAxUeFF5JWBYZEEoEHg8JSQcJGk4%3D"/>
-    <hyperlink ref="I31" r:id="rId19" display="https://item.szlcsc.com/3180501.html?fromZone=s_s__%2522120r%25200603%2522&amp;spm=sc.gbn.xh4.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=EwQLVQJfFVFYVFdUEwcMBlJTRwMNA1IFEQMIXgcCQFExVlNeRVZcVVJVQFBbXjtW"/>
-    <hyperlink ref="H45" r:id="rId20" display="https://item.szlcsc.com/43270.html?fromZone=s_s__%2522aot470%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=EwQLVQJfFVFYVFdUEwcMBlJTRwMNA1IFEQMIXgcCQFExVlNeRVZcVVBTQVlaVDtW"/>
-    <hyperlink ref="H44" r:id="rId21" display="https://item.szlcsc.com/46911.html?fromZone=s_s__%2522AMS1085cm%2522&amp;spm=sc.gbn.xh2.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=EwQLVQJfFVFYVFdUEwcMBlJTRwMNA1IFEQMIXgcCQFExVlNeRVZcVVBTQVlaVDtW"/>
+    <hyperlink ref="H35" r:id="rId13" display="https://item.szlcsc.com/532372.html?fromZone=s_s__%2522TMC5160%2522&amp;spm=sc.gbn.xh1.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
+    <hyperlink ref="H37" r:id="rId14" display="https://item.szlcsc.com/8568600.html?fromZone=s_s__%2522XDDB-1518%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
+    <hyperlink ref="H38" r:id="rId15" display="https://item.szlcsc.com/44273613.html?fromZone=s_s__%2522XL1509%2522&amp;spm=sc.gbn.xh1.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
+    <hyperlink ref="H39" r:id="rId16" display="https://item.szlcsc.com/545744.html?fromZone=s_s__%2522AM26LV32%2522&amp;spm=sc.gbn.xh1.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
+    <hyperlink ref="I9" r:id="rId17" display="https://item.szlcsc.com/54596843.html?fromZone=s_s__%2522470uF%252F50V%2522&amp;spm=sc.gbn.xh4.zy.n___sc.gbn.hd.ss&amp;lcsc_vid=EwQLVQJfFVFYVFdUEwcMBlJTRwMNA1IFEQMIXgcCQFExVlNeRVZcVldUQ1RZVTsOAxUeFF5JWBYZEEoEHg8JSQcJGk4%3D"/>
+    <hyperlink ref="I31" r:id="rId18" display="https://item.szlcsc.com/3180501.html?fromZone=s_s__%2522120r%25200603%2522&amp;spm=sc.gbn.xh4.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=EwQLVQJfFVFYVFdUEwcMBlJTRwMNA1IFEQMIXgcCQFExVlNeRVZcVVJVQFBbXjtW"/>
+    <hyperlink ref="H45" r:id="rId19" display="https://item.szlcsc.com/43270.html?fromZone=s_s__%2522aot470%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=EwQLVQJfFVFYVFdUEwcMBlJTRwMNA1IFEQMIXgcCQFExVlNeRVZcVVBTQVlaVDtW"/>
+    <hyperlink ref="H44" r:id="rId20" display="https://item.szlcsc.com/46911.html?fromZone=s_s__%2522AMS1085cm%2522&amp;spm=sc.gbn.xh2.zy.n___sc.it.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=EwQLVQJfFVFYVFdUEwcMBlJTRwMNA1IFEQMIXgcCQFExVlNeRVZcVVBTQVlaVDtW"/>
+    <hyperlink ref="H25" r:id="rId21" display="https://item.szlcsc.com/3159229.html?fromZone=s_s__%252250mr%25203w%2522&amp;spm=sc.gbn.xh1.zy.n___sc.gbn.hd.ss&amp;c=SO&amp;qhclickid=5d7fd4ccac5a9837&amp;lcsc_vid=RFZbUFVVFlQIA1dTRAMLAlxSQlRfBQdXRAVcVwBVRVQxVlNeRlZaU1dVQlVbXzsOAxUeFF5JWAIASQYPGQZABAsLWA%3D%3D"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
